--- a/StructureDefinition-open-elis-location.xlsx
+++ b/StructureDefinition-open-elis-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:46:49+00:00</t>
+    <t>2026-03-23T16:01:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-location.xlsx
+++ b/StructureDefinition-open-elis-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:01:57+00:00</t>
+    <t>2026-05-11T11:00:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-location.xlsx
+++ b/StructureDefinition-open-elis-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:00:24+00:00</t>
+    <t>2026-05-11T11:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
